--- a/Teste/Teste6/Planilha_Testes_Unitarios.xlsx
+++ b/Teste/Teste6/Planilha_Testes_Unitarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\Teste\Teste6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\camil\OneDrive\Área de Trabalho\AtividadesTeste\Teste\Teste6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985997A0-0B07-42D1-8CA6-7F86E0AD8AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107D774B-9C72-4F52-AA47-EC90B2BEC1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testes Unitários" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>ID do Teste</t>
   </si>
@@ -147,23 +147,17 @@
     <t>Disciplina Inválida</t>
   </si>
   <si>
-    <t>Programação / JavaScript / '' ''</t>
-  </si>
-  <si>
-    <t>05,04,'' ''</t>
-  </si>
-  <si>
-    <t>05, 04, '' ''</t>
-  </si>
-  <si>
     <t>FALTA TERMINAR</t>
+  </si>
+  <si>
+    <t>Ola mundo!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +189,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -268,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -283,31 +283,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -672,7 +681,7 @@
       <c r="F2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>45929</v>
       </c>
       <c r="H2" s="5" t="s">
@@ -699,7 +708,7 @@
       <c r="F3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>45929</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -726,7 +735,7 @@
       <c r="F4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>45929</v>
       </c>
       <c r="H4" s="5" t="s">
@@ -735,38 +744,38 @@
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" ht="15.75">
-      <c r="A5" s="6">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="C5" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="D5" s="14">
+        <v>4</v>
+      </c>
+      <c r="E5" s="14">
+        <v>4</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="9">
         <v>45929</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="12" t="s">
         <v>24</v>
       </c>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" ht="15.75">
-      <c r="A6" s="6"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -775,11 +784,11 @@
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" ht="15.75">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -788,11 +797,11 @@
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" ht="15.75">
-      <c r="A8" s="6"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="10"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -801,11 +810,11 @@
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" ht="15.75">
-      <c r="A9" s="6"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -814,11 +823,11 @@
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" ht="15.75">
-      <c r="A10" s="6"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="11"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -836,11 +845,11 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="4:4">
-      <c r="D23" s="14"/>
+      <c r="D23" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/Teste/Teste6/Planilha_Testes_Unitarios.xlsx
+++ b/Teste/Teste6/Planilha_Testes_Unitarios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\camil\OneDrive\Área de Trabalho\AtividadesTeste\Teste\Teste6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\AtividadesTeste\Teste\Teste6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107D774B-9C72-4F52-AA47-EC90B2BEC1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C85694B-811B-40CE-AA42-F7FDA550087B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testes Unitários" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
   <si>
     <t>ID do Teste</t>
   </si>
@@ -145,9 +145,6 @@
   </si>
   <si>
     <t>Disciplina Inválida</t>
-  </si>
-  <si>
-    <t>FALTA TERMINAR</t>
   </si>
   <si>
     <t>Ola mundo!</t>
@@ -305,16 +302,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -332,6 +329,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>458089</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>181217</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87B2D526-50F6-4428-592D-9802C301D3FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="800100" y="2162175"/>
+          <a:ext cx="6373114" cy="1733792"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -750,13 +796,13 @@
       <c r="B5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="14">
+      <c r="C5" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="17">
         <v>4</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="17">
         <v>4</v>
       </c>
       <c r="F5" s="12" t="s">
@@ -775,7 +821,7 @@
       <c r="B6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="16"/>
+      <c r="C6" s="15"/>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
@@ -788,7 +834,7 @@
       <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="16"/>
+      <c r="C7" s="15"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -801,7 +847,7 @@
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="16"/>
+      <c r="C8" s="15"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -814,7 +860,7 @@
       <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="16"/>
+      <c r="C9" s="15"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -827,7 +873,7 @@
       <c r="B10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="17"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -841,11 +887,6 @@
     <row r="15" spans="1:9">
       <c r="C15" s="2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="B16" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="23" spans="4:4">
@@ -863,5 +904,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>